--- a/README-index/ig/CdaTELToContactPointConceptMap.xlsx
+++ b/README-index/ig/CdaTELToContactPointConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T13:54:13+00:00</t>
+    <t>2026-07-17T13:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/README-index/ig/CdaTELToContactPointConceptMap.xlsx
+++ b/README-index/ig/CdaTELToContactPointConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T13:55:26+00:00</t>
+    <t>2026-07-17T14:00:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/README-index/ig/CdaTELToContactPointConceptMap.xlsx
+++ b/README-index/ig/CdaTELToContactPointConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T14:00:12+00:00</t>
+    <t>2026-07-17T14:15:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
